--- a/DateBase/orders/Nhat 48_2026-9-21.xlsx
+++ b/DateBase/orders/Nhat 48_2026-9-21.xlsx
@@ -790,6 +790,9 @@
       <c r="G2" t="str">
         <v>0541171031551571015131510610105451055102010151081010145</v>
       </c>
+      <c r="H2" t="str">
+        <v>CNY</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
